--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32692,7 +32692,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36892,7 +36892,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16284,7 +16284,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19744,7 +19744,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -21128,7 +21128,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22512,7 +22512,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24736,7 +24736,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25428,7 +25428,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -31012,7 +31012,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32692,7 +32692,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33532,7 +33532,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36892,7 +36892,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39412,7 +39412,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1303,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1696,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1853,9 +1841,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2249,9 +2234,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2397,9 +2379,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2793,9 +2772,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2917,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3337,9 +3310,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3485,9 +3455,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3881,9 +3848,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +3993,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4425,9 +4386,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4573,9 +4531,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4969,9 +4924,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5069,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.004927445823965027</v>
       </c>
@@ -5513,9 +5462,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5661,9 +5607,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6057,9 +6000,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6145,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6601,9 +6538,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6749,9 +6683,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7145,9 +7076,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7293,9 +7221,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7689,9 +7614,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7759,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8233,9 +8152,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -8381,9 +8297,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8777,9 +8690,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8925,9 +8835,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9321,9 +9228,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9469,9 +9373,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9865,9 +9766,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10013,9 +9911,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10409,9 +10304,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10557,9 +10449,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10953,9 +10842,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11101,9 +10987,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -11497,9 +11380,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11645,9 +11525,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -12041,9 +11918,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12189,9 +12063,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12585,9 +12456,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12733,9 +12601,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13129,9 +12994,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13277,9 +13139,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13673,9 +13532,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13821,9 +13677,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14365,9 +14218,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14661,9 +14511,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15205,9 +15052,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15353,9 +15197,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15897,9 +15738,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16045,9 +15883,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16589,9 +16424,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16737,9 +16569,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17281,9 +17110,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17429,9 +17255,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.004772233579740456</v>
       </c>
@@ -17973,9 +17796,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -18121,9 +17941,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18665,9 +18482,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18813,9 +18627,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19357,9 +19168,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19505,9 +19313,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -20049,9 +19854,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20197,9 +19999,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20741,9 +20540,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20889,9 +20685,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -21433,9 +21226,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -21581,9 +21371,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22125,9 +21912,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22273,9 +22057,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -22817,9 +22598,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -23113,9 +22891,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.004679328320790043</v>
       </c>
@@ -23657,9 +23432,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -23805,9 +23577,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -24349,9 +24118,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -24497,9 +24263,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25041,9 +24804,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -25189,9 +24949,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -25733,9 +25490,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -25881,9 +25635,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26425,9 +26176,6 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
@@ -26573,9 +26321,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27265,9 +27010,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -27413,9 +27155,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -28105,9 +27844,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -28253,9 +27989,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0</v>
       </c>
@@ -28945,9 +28678,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29093,9 +28823,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -29785,9 +29512,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -29933,9 +29657,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30625,9 +30346,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -30773,9 +30491,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -31465,9 +31180,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -31613,9 +31325,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -32305,9 +32014,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -32453,9 +32159,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -33145,9 +32848,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33293,9 +32993,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -33985,9 +33682,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -34133,9 +33827,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -34825,9 +34516,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -34973,9 +34661,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -35665,9 +35350,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -35813,9 +35495,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -36505,9 +36184,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -36653,9 +36329,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -37345,9 +37018,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -37493,9 +37163,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -38185,9 +37852,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -38333,9 +37997,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -39025,9 +38686,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0</v>
       </c>
@@ -39173,9 +38831,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -39865,9 +39520,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -40013,9 +39665,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -40705,9 +40354,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -40853,9 +40499,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -41543,9 +41186,6 @@
         <v>0</v>
       </c>
       <c r="O237" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q237" t="n">
         <v>0</v>
       </c>
       <c r="R237" t="n">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -17501,7 +17501,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -18187,7 +18187,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -18873,7 +18873,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -20245,7 +20245,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -23137,7 +23137,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -25195,7 +25195,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -25881,7 +25881,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -27401,7 +27401,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -28235,7 +28235,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -29903,7 +29903,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -31571,7 +31571,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -32405,7 +32405,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN184" t="b">
@@ -33239,7 +33239,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -34907,7 +34907,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -35741,7 +35741,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -36575,7 +36575,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -37409,7 +37409,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -38243,7 +38243,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -39911,7 +39911,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -40745,7 +40745,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN234" t="b">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26557,7 +26557,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30727,7 +30727,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31561,7 +31561,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34063,7 +34063,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36565,7 +36565,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37399,7 +37399,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38233,7 +38233,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39067,7 +39067,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39901,7 +39901,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26557,7 +26557,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30727,7 +30727,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31561,7 +31561,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34063,7 +34063,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36565,7 +36565,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37399,7 +37399,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38233,7 +38233,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39067,7 +39067,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39901,7 +39901,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">

--- a/diseases/d168/2005-2009.xlsx
+++ b/diseases/d168/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -16805,7 +16805,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20235,7 +20235,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -21607,7 +21607,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -25871,7 +25871,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -26557,7 +26557,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -27391,7 +27391,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -28225,7 +28225,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -29893,7 +29893,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -30727,7 +30727,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -31561,7 +31561,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -33229,7 +33229,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -34063,7 +34063,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK194" t="inlineStr">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -36565,7 +36565,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -37399,7 +37399,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -38233,7 +38233,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -39067,7 +39067,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -39901,7 +39901,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -40735,7 +40735,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
